--- a/data/trans_orig/IP25B02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20631</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34962</t>
+          <t>35788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41954</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64524</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25239</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>44176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39811</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52937</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>78991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88341</t>
+          <t>90275</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55631</t>
+          <t>54246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>70428</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>151231</t>
+          <t>149719</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>41025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29877</t>
+          <t>29278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44929</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84939</t>
+          <t>84436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38349</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>40361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37282</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70332</t>
+          <t>69946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47349</t>
+          <t>47692</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29282</t>
+          <t>29347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21288</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35213</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>14296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>41396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27135</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>34096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>51176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43137</t>
+          <t>44972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44215</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>20376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34274</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31513</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21952</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39566</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>20057</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39420</t>
+          <t>39221</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,13%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22909</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44582</t>
+          <t>45486</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>25318</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25523</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18761</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>34940</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>69801</t>
+          <t>70798</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>65181</t>
+          <t>66122</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>97595</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37710</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43429</t>
+          <t>43069</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>68246</t>
+          <t>68087</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35443</t>
+          <t>35621</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28781</t>
+          <t>29237</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>80797</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23536</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43083</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>59172</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>59603</t>
+          <t>59356</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>45602</t>
+          <t>48015</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>68174</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>92465</t>
+          <t>92359</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>120918</t>
+          <t>122574</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>39116</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>59073</t>
+          <t>57956</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>52967</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>75042</t>
+          <t>73852</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>99574</t>
+          <t>98899</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>129465</t>
+          <t>128237</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>46823</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>70656</t>
+          <t>70298</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>85106</t>
+          <t>86264</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>187396</t>
+          <t>218937</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>126639</t>
+          <t>124530</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>185511</t>
+          <t>188601</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>225799</t>
+          <t>228551</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>341460</t>
+          <t>359144</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>139243</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>189588</t>
+          <t>186463</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>175655</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>223244</t>
+          <t>221746</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>331008</t>
+          <t>328278</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>395008</t>
+          <t>398350</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>150845</t>
+          <t>150418</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>198535</t>
+          <t>198701</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>193036</t>
+          <t>194750</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>241405</t>
+          <t>242104</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,47 +5558,47 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>32,15%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>393865</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>359621</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>426414</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>25,64%</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>393865</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>357658</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>430058</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>25,5%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>167760</t>
+          <t>169819</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>219397</t>
+          <t>218479</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>162605</t>
+          <t>165842</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>204902</t>
+          <t>207439</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>345622</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>414485</t>
+          <t>411655</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos en fines de semana / solo 2023 en 2023 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos en fin de semana en 2023 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5455</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2790</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6818</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11611</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17517</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12025</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6781</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20689</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>20997</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37701</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23903</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17810</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29756</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>46,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24381</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16250</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33408</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41482</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63330</t>
+          <t>53143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23176</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17738</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29993</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33615</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24983</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44176</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,17%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>46902</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53349</t>
+          <t>39163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78991</t>
+          <t>55661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>72811</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72811</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72811</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56066</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>152177</t>
+          <t>120211</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152177</t>
+          <t>120211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152177</t>
+          <t>120211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38518</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28732</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49442</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>42,92%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>53552</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30494</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>90275</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54246</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>94709</t>
+          <t>68842</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>70428</t>
+          <t>55885</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>149719</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36972</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27340</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47385</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28225</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12932</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41025</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39806</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>33474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68031</t>
+          <t>62301</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>51309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84436</t>
+          <t>75270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23942</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16474</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37724</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26905</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12968</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>38602</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40361</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53786</t>
+          <t>51112</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>39116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69946</t>
+          <t>65237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15759</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22458</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8487</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25506</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>23481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35537</t>
+          <t>31912</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115191</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>115191</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>115191</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>125233</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125233</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125233</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>252063</t>
+          <t>214166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252063</t>
+          <t>214166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252063</t>
+          <t>214166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8624</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14461</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11567</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7295</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16941</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13753</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9604</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>19813</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>23,39%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16,34%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>33,7%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12150</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>7533</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>16981</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>21,0%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27349</t>
+          <t>25833</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35601</t>
+          <t>33215</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18325</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13342</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24433</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>22,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13186</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8478</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18361</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>17846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18091</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13477</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23536</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20969</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16026</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26739</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36,23%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>42273</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51176</t>
+          <t>46377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>58794</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>58794</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>58794</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>57872</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>57872</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57872</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66572</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66572</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66572</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>114998</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>114998</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>114998</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>23843</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13529</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>39215</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>35,04%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>57,63%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9487</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4626</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>16181</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44972</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>35749</t>
+          <t>33777</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23174</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>54785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16287</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9470</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>25088</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>36,87%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>15112</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9660</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>21697</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>23,63%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>23363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32392</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43258</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13336</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>21129</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>11947</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>6880</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>18150</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>28,37%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36095</t>
+          <t>34660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14578</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7968</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>23761</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>27419</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20376</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>34787</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>42,87%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>34902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>42024</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31142</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56399</t>
+          <t>54088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>68044</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>68044</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>68044</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>63966</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>63966</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>63966</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>74153</t>
+          <t>64913</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74153</t>
+          <t>64913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74153</t>
+          <t>64913</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>138119</t>
+          <t>132958</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>138119</t>
+          <t>132958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138119</t>
+          <t>132958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,107 +2996,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3394</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>3713</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7462</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>12998</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>32,84%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3731</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>8102</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>13782</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>14696</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10338</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19559</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>37,13%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>17679</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>13395</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>21544</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>62,42%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19696</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>32818</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26241</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39221</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,72 +3565,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>10249</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20,94%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>8393</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>4892</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>13078</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30045</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45486</t>
+          <t>42846</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>15370</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>7264</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>4148</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>11737</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>17973</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -3904,72 +3904,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>15760</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11651</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>20931</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>32,2%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>23,81%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>42,77%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>12479</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>8372</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>17743</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25523</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>26914</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40802</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>48900</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>38200</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>60702</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>35,36%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>27,62%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>24957</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>18551</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>33203</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>21,07%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>28,03%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>54695</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>70798</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>79652</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>66122</t>
+          <t>62042</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>97120</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>24963</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>17238</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>34483</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>28104</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>20468</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>36409</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>23,73%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>37426</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>54640</t>
+          <t>53383</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>42280</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>68087</t>
+          <t>66067</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>34943</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>26022</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>45164</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>32,66%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>25901</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>18239</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>35621</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>30,07%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51842</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>65068</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>52818</t>
+          <t>47178</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>80797</t>
+          <t>72683</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>29481</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>21434</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>38557</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>39494</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>31258</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>48175</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>33,34%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>26,39%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>40,67%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>37544</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>45886</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>71840</t>
+          <t>67025</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>59172</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>87233</t>
+          <t>80480</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>138287</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>138287</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>138287</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>118455</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>118455</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>118455</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>152746</t>
+          <t>116676</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>152746</t>
+          <t>116676</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>152746</t>
+          <t>116676</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>271201</t>
+          <t>254964</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>271201</t>
+          <t>254964</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>271201</t>
+          <t>254964</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4703,72 +4703,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>5856</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>12066</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>3270</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>7497</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -4816,72 +4816,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>59891</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>48721</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>70719</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>37,64%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>44,44%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>49735</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>40171</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>59356</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>45,51%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>57388</t>
+          <t>54462</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>48015</t>
+          <t>43915</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>68753</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>107123</t>
+          <t>114353</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>92359</t>
+          <t>98545</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>122574</t>
+          <t>128536</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -4929,72 +4929,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>66042</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>55567</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>77352</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>48,61%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>48985</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>39116</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>57956</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>37,56%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>44,44%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>63844</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>52967</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>73852</t>
+          <t>64284</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>112829</t>
+          <t>119352</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>98899</t>
+          <t>104699</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>134619</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -5042,72 +5042,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>27328</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>19936</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>35779</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>17,17%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>28424</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>21040</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>37072</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>21,8%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>16,13%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>58123</t>
+          <t>55596</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>70298</t>
+          <t>68036</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -5155,57 +5155,57 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>130413</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>130413</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>130413</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>286850</t>
+          <t>298565</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>286850</t>
+          <t>298565</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>286850</t>
+          <t>298565</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5272,72 +5272,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>138329</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>116632</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>167913</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>114015</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>86264</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>218937</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>151628</t>
+          <t>92464</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>124530</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>188601</t>
+          <t>109104</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>265643</t>
+          <t>230793</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>228551</t>
+          <t>204123</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>359144</t>
+          <t>264423</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -5385,72 +5385,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>187796</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>166155</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>210546</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>164409</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>139243</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>186463</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>197947</t>
+          <t>165472</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>147236</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>221746</t>
+          <t>185905</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>362356</t>
+          <t>353268</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>325779</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>398350</t>
+          <t>382807</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -5498,72 +5498,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>205265</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>183932</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>230498</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>176249</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>150418</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>198701</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>27,14%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>30,6%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>217616</t>
+          <t>175606</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>194750</t>
+          <t>158952</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>242104</t>
+          <t>195763</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>393865</t>
+          <t>380870</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>359621</t>
+          <t>353107</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>426414</t>
+          <t>412017</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -5611,72 +5611,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>160712</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>143086</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>179366</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>194756</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>169819</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>218479</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>185818</t>
+          <t>180114</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>165842</t>
+          <t>163510</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>207439</t>
+          <t>200514</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>380574</t>
+          <t>340826</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>314655</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>411655</t>
+          <t>369055</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -5724,57 +5724,57 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
